--- a/SRC_BAPIv2.2_TABLEDATA_OUTPUT_E/SetInfo/Sample_LoginSetting.xlsx
+++ b/SRC_BAPIv2.2_TABLEDATA_OUTPUT_E/SetInfo/Sample_LoginSetting.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E424EC-9A31-4849-81C6-BDC2C35FF8A6}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B02993-587D-4CE3-9F8E-B1477FCDCA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1080" yWindow="-21165" windowWidth="31410" windowHeight="17895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2670" yWindow="1965" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>in_AppServer</t>
     <phoneticPr fontId="2"/>
@@ -78,29 +78,45 @@
     <t>SRC_Common\SRC_RFC_READ_TABLE_v2.2.xaml</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>10.10.10.6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>310</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -138,16 +154,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -426,14 +442,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="52.375" customWidth="1"/>
-    <col min="3" max="3" width="59.25" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="52.42578125" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
@@ -444,43 +460,51 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="93.75">
+    <row r="6" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -499,21 +523,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C827732D69AAF14BA01846CE3CC7794A" ma:contentTypeVersion="7" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7967a75d26f026d2956a0c454cdd2b11">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0bc06b84-8904-4b80-b12f-bdecd9bbb428" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8152c92a3439d77e4b3ac6373a0ad55f" ns2:_="">
     <xsd:import namespace="0bc06b84-8904-4b80-b12f-bdecd9bbb428"/>
@@ -677,24 +686,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A77ACE8-AE73-425A-9A36-418F5227C274}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62AE6295-7F1E-4952-BEE5-0B134F7C8027}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191C9D74-0C5C-401D-9018-9CFFC9A36C3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -710,4 +717,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62AE6295-7F1E-4952-BEE5-0B134F7C8027}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A77ACE8-AE73-425A-9A36-418F5227C274}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>